--- a/util/Validation/ToolValidation/FeatureEnvyValidationForTool.xlsx
+++ b/util/Validation/ToolValidation/FeatureEnvyValidationForTool.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neda/Documents/workspace/DissertationProject/util/Validation/ToolValidation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{539952CE-5D17-8F42-8304-5D472777F4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B5F8A99-A083-6E47-A224-BF45EE4E4FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="460" windowWidth="25440" windowHeight="14060"/>
+    <workbookView xWindow="28980" yWindow="460" windowWidth="25040" windowHeight="13760"/>
   </bookViews>
   <sheets>
     <sheet name="FeatureEnvyValidationForTool" sheetId="1" r:id="rId1"/>
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -2954,10 +2954,10 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -3256,7 +3256,7 @@
         <v>5</v>
       </c>
       <c r="E16">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
@@ -3296,13 +3296,13 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
@@ -3408,19 +3408,19 @@
         <v>36</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="s">
         <v>33</v>
@@ -3454,16 +3454,16 @@
         <v>38</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
@@ -3500,16 +3500,16 @@
         <v>40</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -3523,16 +3523,16 @@
         <v>41</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>42</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         <v>43</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
@@ -3641,13 +3641,13 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
@@ -3684,16 +3684,16 @@
         <v>50</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
@@ -3707,16 +3707,16 @@
         <v>51</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E36">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
@@ -3733,16 +3733,16 @@
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="s">
         <v>53</v>
@@ -3799,16 +3799,16 @@
         <v>57</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
@@ -3848,13 +3848,13 @@
         <v>1</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F42" t="b">
         <v>0</v>
@@ -3868,16 +3868,16 @@
         <v>61</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F43" t="b">
         <v>0</v>
@@ -3917,13 +3917,13 @@
         <v>0</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -3969,7 +3969,7 @@
         <v>34</v>
       </c>
       <c r="E47">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -4121,16 +4121,16 @@
         <v>77</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
@@ -4144,16 +4144,16 @@
         <v>78</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F55" t="b">
         <v>0</v>
@@ -4190,16 +4190,16 @@
         <v>81</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
@@ -4627,19 +4627,19 @@
         <v>103</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="s">
         <v>87</v>
@@ -4659,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F77" t="b">
         <v>0</v>
@@ -4889,7 +4889,7 @@
         <v>3</v>
       </c>
       <c r="E87">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F87" t="b">
         <v>0</v>
@@ -5280,7 +5280,7 @@
         <v>5</v>
       </c>
       <c r="E104">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F104" t="b">
         <v>1</v>
@@ -5294,16 +5294,16 @@
         <v>132</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
         <v>5</v>
-      </c>
-      <c r="E105">
-        <v>46</v>
       </c>
       <c r="F105" t="b">
         <v>0</v>
@@ -5395,7 +5395,7 @@
         <v>2</v>
       </c>
       <c r="E109">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F109" t="b">
         <v>0</v>
@@ -5504,13 +5504,13 @@
         <v>1</v>
       </c>
       <c r="C114">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F114" t="b">
         <v>0</v>
@@ -5596,13 +5596,13 @@
         <v>1</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" t="b">
         <v>0</v>
@@ -5619,13 +5619,13 @@
         <v>1</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F119" t="b">
         <v>0</v>
@@ -5734,13 +5734,13 @@
         <v>1</v>
       </c>
       <c r="C124">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D124">
         <v>0</v>
       </c>
       <c r="E124">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F124" t="b">
         <v>0</v>
@@ -5809,7 +5809,7 @@
         <v>1</v>
       </c>
       <c r="E127">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F127" t="b">
         <v>0</v>
@@ -5901,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F131" t="b">
         <v>0</v>
@@ -6467,16 +6467,16 @@
         <v>187</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D156">
         <v>0</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F156" t="b">
         <v>0</v>
@@ -6493,13 +6493,13 @@
         <v>0</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D157">
         <v>0</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F157" t="b">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>189</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D158">
         <v>0</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F158" t="b">
         <v>0</v>
@@ -6536,16 +6536,16 @@
         <v>191</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F159" t="b">
         <v>0</v>
@@ -6562,13 +6562,13 @@
         <v>0</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F160" t="b">
         <v>0</v>
@@ -6585,13 +6585,13 @@
         <v>0</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F161" t="b">
         <v>0</v>
@@ -6608,16 +6608,16 @@
         <v>0</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162" t="s">
         <v>190</v>
@@ -6631,16 +6631,16 @@
         <v>0</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="F163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G163" t="s">
         <v>190</v>
@@ -6660,7 +6660,7 @@
         <v>14</v>
       </c>
       <c r="E164">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F164" t="b">
         <v>0</v>
@@ -6683,7 +6683,7 @@
         <v>4</v>
       </c>
       <c r="E165">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F165" t="b">
         <v>1</v>
@@ -6706,7 +6706,7 @@
         <v>10</v>
       </c>
       <c r="E166">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F166" t="b">
         <v>1</v>
@@ -7068,13 +7068,13 @@
         <v>1</v>
       </c>
       <c r="C182">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D182">
         <v>2</v>
       </c>
       <c r="E182">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F182" t="b">
         <v>0</v>
@@ -7183,13 +7183,13 @@
         <v>1</v>
       </c>
       <c r="C187">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D187">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E187">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="F187" t="b">
         <v>1</v>
@@ -7235,7 +7235,7 @@
         <v>1</v>
       </c>
       <c r="E189">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F189" t="b">
         <v>0</v>
@@ -7275,13 +7275,13 @@
         <v>0</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F191" t="b">
         <v>0</v>
@@ -7459,13 +7459,13 @@
         <v>1</v>
       </c>
       <c r="C199">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D199">
         <v>5</v>
       </c>
       <c r="E199">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="F199" t="b">
         <v>1</v>
@@ -7482,13 +7482,13 @@
         <v>1</v>
       </c>
       <c r="C200">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D200">
         <v>25</v>
       </c>
       <c r="E200">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F200" t="b">
         <v>1</v>
@@ -7502,16 +7502,16 @@
         <v>256</v>
       </c>
       <c r="B201">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C201">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D201">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E201">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="F201" t="b">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>1</v>
       </c>
       <c r="C204">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D204">
         <v>21</v>
       </c>
       <c r="E204">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F204" t="b">
         <v>1</v>
@@ -7689,13 +7689,13 @@
         <v>1</v>
       </c>
       <c r="C209">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D209">
         <v>6</v>
       </c>
       <c r="E209">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F209" t="b">
         <v>1</v>
@@ -7827,13 +7827,13 @@
         <v>0</v>
       </c>
       <c r="C215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D215">
         <v>0</v>
       </c>
       <c r="E215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F215" t="b">
         <v>0</v>
@@ -7873,13 +7873,13 @@
         <v>0</v>
       </c>
       <c r="C217">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D217">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E217">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F217" t="b">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0</v>
       </c>
       <c r="C218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F218" t="b">
         <v>0</v>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="C219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D219">
         <v>0</v>
       </c>
       <c r="E219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F219" t="b">
         <v>0</v>
@@ -7965,13 +7965,13 @@
         <v>0</v>
       </c>
       <c r="C221">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E221">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F221" t="b">
         <v>0</v>
@@ -7988,13 +7988,13 @@
         <v>1</v>
       </c>
       <c r="C222">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D222">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E222">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F222" t="b">
         <v>1</v>
@@ -8014,10 +8014,10 @@
         <v>19</v>
       </c>
       <c r="D223">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E223">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F223" t="b">
         <v>1</v>
@@ -8057,13 +8057,13 @@
         <v>1</v>
       </c>
       <c r="C225">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D225">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E225">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F225" t="b">
         <v>0</v>
@@ -8080,13 +8080,13 @@
         <v>0</v>
       </c>
       <c r="C226">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D226">
         <v>0</v>
       </c>
       <c r="E226">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F226" t="b">
         <v>0</v>
@@ -8103,13 +8103,13 @@
         <v>0</v>
       </c>
       <c r="C227">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D227">
         <v>0</v>
       </c>
       <c r="E227">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F227" t="b">
         <v>0</v>
@@ -8126,13 +8126,13 @@
         <v>0</v>
       </c>
       <c r="C228">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D228">
         <v>0</v>
       </c>
       <c r="E228">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F228" t="b">
         <v>0</v>
@@ -8152,10 +8152,10 @@
         <v>2</v>
       </c>
       <c r="D229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E229">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F229" t="b">
         <v>0</v>
@@ -8169,16 +8169,16 @@
         <v>304</v>
       </c>
       <c r="B230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C230">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E230">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F230" t="b">
         <v>0</v>
@@ -8195,13 +8195,13 @@
         <v>0</v>
       </c>
       <c r="C231">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D231">
         <v>0</v>
       </c>
       <c r="E231">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F231" t="b">
         <v>0</v>
@@ -8310,13 +8310,13 @@
         <v>1</v>
       </c>
       <c r="C236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E236">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F236" t="b">
         <v>0</v>
@@ -8333,13 +8333,13 @@
         <v>1</v>
       </c>
       <c r="C237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D237">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E237">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F237" t="b">
         <v>0</v>
@@ -8356,13 +8356,13 @@
         <v>1</v>
       </c>
       <c r="C238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F238" t="b">
         <v>0</v>
@@ -8379,13 +8379,13 @@
         <v>1</v>
       </c>
       <c r="C239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D239">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E239">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F239" t="b">
         <v>0</v>
@@ -8402,13 +8402,13 @@
         <v>1</v>
       </c>
       <c r="C240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E240">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F240" t="b">
         <v>0</v>
@@ -8448,13 +8448,13 @@
         <v>2</v>
       </c>
       <c r="C242">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D242">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E242">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F242" t="b">
         <v>0</v>
@@ -8517,13 +8517,13 @@
         <v>0</v>
       </c>
       <c r="C245">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E245">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F245" t="b">
         <v>0</v>
@@ -8546,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="E246">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F246" t="b">
         <v>0</v>
@@ -8586,13 +8586,13 @@
         <v>0</v>
       </c>
       <c r="C248">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D248">
         <v>0</v>
       </c>
       <c r="E248">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F248" t="b">
         <v>0</v>
@@ -8609,13 +8609,13 @@
         <v>0</v>
       </c>
       <c r="C249">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E249">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F249" t="b">
         <v>0</v>
@@ -8632,13 +8632,13 @@
         <v>1</v>
       </c>
       <c r="C250">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D250">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E250">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F250" t="b">
         <v>0</v>
@@ -8675,16 +8675,16 @@
         <v>333</v>
       </c>
       <c r="B252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C252">
         <v>1</v>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E252">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F252" t="b">
         <v>0</v>
@@ -8698,16 +8698,16 @@
         <v>334</v>
       </c>
       <c r="B253">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D253">
         <v>0</v>
       </c>
       <c r="E253">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F253" t="b">
         <v>0</v>
@@ -8724,13 +8724,13 @@
         <v>0</v>
       </c>
       <c r="C254">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D254">
         <v>0</v>
       </c>
       <c r="E254">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F254" t="b">
         <v>0</v>
@@ -8753,7 +8753,7 @@
         <v>0</v>
       </c>
       <c r="E255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F255" t="b">
         <v>0</v>
@@ -8776,7 +8776,7 @@
         <v>0</v>
       </c>
       <c r="E256">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F256" t="b">
         <v>0</v>
@@ -8793,13 +8793,13 @@
         <v>0</v>
       </c>
       <c r="C257">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E257">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F257" t="b">
         <v>0</v>
@@ -8836,7 +8836,7 @@
         <v>342</v>
       </c>
       <c r="B259">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>343</v>
       </c>
       <c r="B260">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -8882,7 +8882,7 @@
         <v>344</v>
       </c>
       <c r="B261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -8905,16 +8905,16 @@
         <v>345</v>
       </c>
       <c r="B262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C262">
         <v>0</v>
       </c>
       <c r="D262">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E262">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F262" t="b">
         <v>0</v>
@@ -8983,7 +8983,7 @@
         <v>0</v>
       </c>
       <c r="E265">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F265" t="b">
         <v>0</v>
@@ -9000,13 +9000,13 @@
         <v>0</v>
       </c>
       <c r="C266">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D266">
         <v>0</v>
       </c>
       <c r="E266">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F266" t="b">
         <v>0</v>
@@ -9112,16 +9112,16 @@
         <v>358</v>
       </c>
       <c r="B271">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
         <v>2</v>
       </c>
-      <c r="D271">
-        <v>1</v>
-      </c>
       <c r="E271">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F271" t="b">
         <v>0</v>
@@ -9161,13 +9161,13 @@
         <v>0</v>
       </c>
       <c r="C273">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D273">
         <v>0</v>
       </c>
       <c r="E273">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F273" t="b">
         <v>0</v>
@@ -9204,16 +9204,16 @@
         <v>363</v>
       </c>
       <c r="B275">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C275">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D275">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E275">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F275" t="b">
         <v>0</v>
@@ -9279,10 +9279,10 @@
         <v>0</v>
       </c>
       <c r="D278">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E278">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F278" t="b">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E279">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F279" t="b">
         <v>0</v>
@@ -9322,13 +9322,13 @@
         <v>0</v>
       </c>
       <c r="C280">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D280">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E280">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F280" t="b">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         <v>1</v>
       </c>
       <c r="C285">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D285">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E285">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F285" t="b">
         <v>0</v>
@@ -9549,16 +9549,16 @@
         <v>381</v>
       </c>
       <c r="B290">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C290">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D290">
         <v>0</v>
       </c>
       <c r="E290">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F290" t="b">
         <v>0</v>
@@ -9572,16 +9572,16 @@
         <v>382</v>
       </c>
       <c r="B291">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C291">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D291">
         <v>0</v>
       </c>
       <c r="E291">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F291" t="b">
         <v>0</v>
@@ -9595,16 +9595,16 @@
         <v>383</v>
       </c>
       <c r="B292">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C292">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D292">
         <v>0</v>
       </c>
       <c r="E292">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F292" t="b">
         <v>0</v>
@@ -9618,16 +9618,16 @@
         <v>384</v>
       </c>
       <c r="B293">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C293">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D293">
         <v>0</v>
       </c>
       <c r="E293">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F293" t="b">
         <v>0</v>
@@ -9641,16 +9641,16 @@
         <v>385</v>
       </c>
       <c r="B294">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C294">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D294">
         <v>0</v>
       </c>
       <c r="E294">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F294" t="b">
         <v>0</v>
@@ -9664,7 +9664,7 @@
         <v>386</v>
       </c>
       <c r="B295">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C295">
         <v>0</v>
@@ -9690,13 +9690,13 @@
         <v>1</v>
       </c>
       <c r="C296">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D296">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E296">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F296" t="b">
         <v>0</v>
@@ -9713,13 +9713,13 @@
         <v>1</v>
       </c>
       <c r="C297">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D297">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E297">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F297" t="b">
         <v>1</v>
@@ -9736,13 +9736,13 @@
         <v>1</v>
       </c>
       <c r="C298">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E298">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F298" t="b">
         <v>0</v>
@@ -9756,16 +9756,16 @@
         <v>390</v>
       </c>
       <c r="B299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C299">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E299">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F299" t="b">
         <v>0</v>
@@ -9779,16 +9779,16 @@
         <v>391</v>
       </c>
       <c r="B300">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>2</v>
+      </c>
+      <c r="E300">
         <v>10</v>
-      </c>
-      <c r="D300">
-        <v>1</v>
-      </c>
-      <c r="E300">
-        <v>20</v>
       </c>
       <c r="F300" t="b">
         <v>0</v>
@@ -9805,13 +9805,13 @@
         <v>1</v>
       </c>
       <c r="C301">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D301">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="E301">
-        <v>587</v>
+        <v>526</v>
       </c>
       <c r="F301" t="b">
         <v>1</v>
@@ -9828,13 +9828,13 @@
         <v>1</v>
       </c>
       <c r="C302">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D302">
         <v>2</v>
       </c>
       <c r="E302">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F302" t="b">
         <v>0</v>
@@ -9851,13 +9851,13 @@
         <v>1</v>
       </c>
       <c r="C303">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D303">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E303">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F303" t="b">
         <v>1</v>
@@ -9877,10 +9877,10 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E304">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F304" t="b">
         <v>1</v>
@@ -9894,16 +9894,16 @@
         <v>396</v>
       </c>
       <c r="B305">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C305">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D305">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E305">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F305" t="b">
         <v>0</v>
@@ -9917,16 +9917,16 @@
         <v>397</v>
       </c>
       <c r="B306">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C306">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D306">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E306">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F306" t="b">
         <v>0</v>
@@ -9943,16 +9943,16 @@
         <v>0</v>
       </c>
       <c r="C307">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D307">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E307">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="F307" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G307" t="s">
         <v>399</v>
@@ -9966,13 +9966,13 @@
         <v>1</v>
       </c>
       <c r="C308">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D308">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E308">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="F308" t="b">
         <v>1</v>
@@ -10495,13 +10495,13 @@
         <v>0</v>
       </c>
       <c r="C331">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D331">
         <v>0</v>
       </c>
       <c r="E331">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F331" t="b">
         <v>0</v>
@@ -10518,13 +10518,13 @@
         <v>0</v>
       </c>
       <c r="C332">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D332">
         <v>0</v>
       </c>
       <c r="E332">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F332" t="b">
         <v>0</v>
@@ -10768,7 +10768,7 @@
         <v>440</v>
       </c>
       <c r="B343">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C343">
         <v>0</v>
@@ -10955,13 +10955,13 @@
         <v>0</v>
       </c>
       <c r="C351">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D351">
         <v>0</v>
       </c>
       <c r="E351">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F351" t="b">
         <v>0</v>
@@ -11001,13 +11001,13 @@
         <v>0</v>
       </c>
       <c r="C353">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D353">
         <v>0</v>
       </c>
       <c r="E353">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F353" t="b">
         <v>0</v>
@@ -11228,7 +11228,7 @@
         <v>473</v>
       </c>
       <c r="B363">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C363">
         <v>0</v>
@@ -11254,13 +11254,13 @@
         <v>0</v>
       </c>
       <c r="C364">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D364">
         <v>0</v>
       </c>
       <c r="E364">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F364" t="b">
         <v>0</v>
@@ -11297,16 +11297,16 @@
         <v>478</v>
       </c>
       <c r="B366">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C366">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D366">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E366">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F366" t="b">
         <v>0</v>
@@ -11412,16 +11412,16 @@
         <v>485</v>
       </c>
       <c r="B371">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C371">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D371">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E371">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F371" t="b">
         <v>0</v>
@@ -11461,13 +11461,13 @@
         <v>1</v>
       </c>
       <c r="C373">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D373">
         <v>0</v>
       </c>
       <c r="E373">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F373" t="b">
         <v>0</v>
@@ -11576,13 +11576,13 @@
         <v>1</v>
       </c>
       <c r="C378">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D378">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E378">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F378" t="b">
         <v>0</v>
@@ -11596,19 +11596,19 @@
         <v>494</v>
       </c>
       <c r="B379">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C379">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D379">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E379">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F379" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G379" t="s">
         <v>490</v>
@@ -11642,16 +11642,16 @@
         <v>497</v>
       </c>
       <c r="B381">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C381">
+        <v>16</v>
+      </c>
+      <c r="D381">
         <v>3</v>
       </c>
-      <c r="D381">
-        <v>0</v>
-      </c>
       <c r="E381">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F381" t="b">
         <v>0</v>
@@ -11668,13 +11668,13 @@
         <v>0</v>
       </c>
       <c r="C382">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D382">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E382">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F382" t="b">
         <v>0</v>
@@ -11691,13 +11691,13 @@
         <v>0</v>
       </c>
       <c r="C383">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D383">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E383">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F383" t="b">
         <v>0</v>
@@ -11780,19 +11780,19 @@
         <v>504</v>
       </c>
       <c r="B387">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C387">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D387">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E387">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="F387" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G387" t="s">
         <v>499</v>
@@ -11829,16 +11829,16 @@
         <v>0</v>
       </c>
       <c r="C389">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D389">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E389">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F389" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G389" t="s">
         <v>508</v>
@@ -11852,16 +11852,16 @@
         <v>0</v>
       </c>
       <c r="C390">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D390">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E390">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F390" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G390" t="s">
         <v>510</v>
@@ -11875,13 +11875,13 @@
         <v>0</v>
       </c>
       <c r="C391">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D391">
         <v>0</v>
       </c>
       <c r="E391">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F391" t="b">
         <v>0</v>
@@ -11898,13 +11898,13 @@
         <v>1</v>
       </c>
       <c r="C392">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D392">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E392">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F392" t="b">
         <v>0</v>
@@ -11921,13 +11921,13 @@
         <v>1</v>
       </c>
       <c r="C393">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D393">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E393">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F393" t="b">
         <v>0</v>
@@ -11941,16 +11941,16 @@
         <v>515</v>
       </c>
       <c r="B394">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C394">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D394">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E394">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="F394" t="b">
         <v>0</v>
@@ -12010,16 +12010,16 @@
         <v>518</v>
       </c>
       <c r="B397">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C397">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D397">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E397">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F397" t="b">
         <v>0</v>
@@ -12033,16 +12033,16 @@
         <v>519</v>
       </c>
       <c r="B398">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C398">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D398">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E398">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F398" t="b">
         <v>0</v>
@@ -12056,13 +12056,13 @@
         <v>520</v>
       </c>
       <c r="B399">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C399">
         <v>0</v>
       </c>
       <c r="D399">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E399">
         <v>1</v>
@@ -12082,13 +12082,13 @@
         <v>0</v>
       </c>
       <c r="C400">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D400">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E400">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F400" t="b">
         <v>0</v>
@@ -12105,13 +12105,13 @@
         <v>1</v>
       </c>
       <c r="C401">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D401">
         <v>0</v>
       </c>
       <c r="E401">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F401" t="b">
         <v>0</v>
@@ -12125,16 +12125,16 @@
         <v>524</v>
       </c>
       <c r="B402">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C402">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D402">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E402">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F402" t="b">
         <v>0</v>
@@ -12174,13 +12174,13 @@
         <v>0</v>
       </c>
       <c r="C404">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D404">
         <v>0</v>
       </c>
       <c r="E404">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F404" t="b">
         <v>0</v>
@@ -12197,13 +12197,13 @@
         <v>0</v>
       </c>
       <c r="C405">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D405">
         <v>0</v>
       </c>
       <c r="E405">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F405" t="b">
         <v>0</v>
@@ -12220,13 +12220,13 @@
         <v>0</v>
       </c>
       <c r="C406">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D406">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E406">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F406" t="b">
         <v>0</v>
@@ -12263,16 +12263,16 @@
         <v>535</v>
       </c>
       <c r="B408">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C408">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D408">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E408">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F408" t="b">
         <v>0</v>
@@ -12286,16 +12286,16 @@
         <v>537</v>
       </c>
       <c r="B409">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C409">
         <v>0</v>
       </c>
       <c r="D409">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E409">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F409" t="b">
         <v>0</v>
@@ -12309,16 +12309,16 @@
         <v>539</v>
       </c>
       <c r="B410">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C410">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D410">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E410">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F410" t="b">
         <v>0</v>
@@ -12358,13 +12358,13 @@
         <v>1</v>
       </c>
       <c r="C412">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D412">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E412">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F412" t="b">
         <v>1</v>
@@ -12410,7 +12410,7 @@
         <v>25</v>
       </c>
       <c r="E414">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F414" t="b">
         <v>1</v>
@@ -12703,13 +12703,13 @@
         <v>1</v>
       </c>
       <c r="C427">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D427">
         <v>1</v>
       </c>
       <c r="E427">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F427" t="b">
         <v>0</v>
@@ -12749,13 +12749,13 @@
         <v>1</v>
       </c>
       <c r="C429">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D429">
         <v>0</v>
       </c>
       <c r="E429">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F429" t="b">
         <v>0</v>
@@ -12818,13 +12818,13 @@
         <v>1</v>
       </c>
       <c r="C432">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D432">
         <v>0</v>
       </c>
       <c r="E432">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F432" t="b">
         <v>0</v>
@@ -12864,13 +12864,13 @@
         <v>1</v>
       </c>
       <c r="C434">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D434">
         <v>0</v>
       </c>
       <c r="E434">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F434" t="b">
         <v>0</v>
@@ -12976,16 +12976,16 @@
         <v>581</v>
       </c>
       <c r="B439">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C439">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D439">
         <v>0</v>
       </c>
       <c r="E439">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F439" t="b">
         <v>0</v>
@@ -13008,7 +13008,7 @@
         <v>0</v>
       </c>
       <c r="E440">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F440" t="b">
         <v>0</v>
@@ -13117,13 +13117,13 @@
         <v>1</v>
       </c>
       <c r="C445">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D445">
         <v>0</v>
       </c>
       <c r="E445">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F445" t="b">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         <v>1</v>
       </c>
       <c r="C448">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D448">
         <v>0</v>
       </c>
       <c r="E448">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F448" t="b">
         <v>0</v>
@@ -13330,7 +13330,7 @@
         <v>0</v>
       </c>
       <c r="E454">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F454" t="b">
         <v>0</v>
@@ -13353,7 +13353,7 @@
         <v>0</v>
       </c>
       <c r="E455">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F455" t="b">
         <v>0</v>
@@ -13416,13 +13416,13 @@
         <v>1</v>
       </c>
       <c r="C458">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D458">
         <v>0</v>
       </c>
       <c r="E458">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F458" t="b">
         <v>0</v>
@@ -13491,7 +13491,7 @@
         <v>0</v>
       </c>
       <c r="E461">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F461" t="b">
         <v>0</v>
@@ -13537,7 +13537,7 @@
         <v>0</v>
       </c>
       <c r="E463">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F463" t="b">
         <v>0</v>
@@ -13781,16 +13781,16 @@
         <v>627</v>
       </c>
       <c r="B474">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C474">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D474">
         <v>0</v>
       </c>
       <c r="E474">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F474" t="b">
         <v>0</v>
@@ -13928,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="E480">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F480" t="b">
         <v>0</v>
@@ -14060,13 +14060,13 @@
         <v>1</v>
       </c>
       <c r="C486">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D486">
         <v>0</v>
       </c>
       <c r="E486">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F486" t="b">
         <v>0</v>
@@ -14221,13 +14221,13 @@
         <v>1</v>
       </c>
       <c r="C493">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D493">
         <v>0</v>
       </c>
       <c r="E493">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F493" t="b">
         <v>0</v>
@@ -14273,7 +14273,7 @@
         <v>0</v>
       </c>
       <c r="E495">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F495" t="b">
         <v>0</v>
@@ -14359,13 +14359,13 @@
         <v>1</v>
       </c>
       <c r="C499">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D499">
         <v>0</v>
       </c>
       <c r="E499">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F499" t="b">
         <v>0</v>
@@ -14428,13 +14428,13 @@
         <v>1</v>
       </c>
       <c r="C502">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D502">
         <v>0</v>
       </c>
       <c r="E502">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F502" t="b">
         <v>0</v>
@@ -14520,13 +14520,13 @@
         <v>1</v>
       </c>
       <c r="C506">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D506">
         <v>0</v>
       </c>
       <c r="E506">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F506" t="b">
         <v>0</v>
@@ -14641,7 +14641,7 @@
         <v>3</v>
       </c>
       <c r="E511">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F511" t="b">
         <v>0</v>
@@ -14747,7 +14747,7 @@
         <v>677</v>
       </c>
       <c r="B516">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C516">
         <v>0</v>

--- a/util/Validation/ToolValidation/FeatureEnvyValidationForTool.xlsx
+++ b/util/Validation/ToolValidation/FeatureEnvyValidationForTool.xlsx
@@ -8,19 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neda/Documents/workspace/DissertationProject/util/Validation/ToolValidation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B5F8A99-A083-6E47-A224-BF45EE4E4FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{CE211E18-FE3F-FA47-9776-4ED6596AE09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28980" yWindow="460" windowWidth="25040" windowHeight="13760"/>
+    <workbookView xWindow="28400" yWindow="4620" windowWidth="25040" windowHeight="13760"/>
   </bookViews>
   <sheets>
     <sheet name="FeatureEnvyValidationForTool" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FeatureEnvyValidationForTool!$A$1:$G$516</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="689">
   <si>
     <t>Class Name</t>
   </si>
@@ -2054,6 +2069,39 @@
   </si>
   <si>
     <t>ABCArray2</t>
+  </si>
+  <si>
+    <t>Tool</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>FP</t>
+  </si>
+  <si>
+    <t>Precision:</t>
+  </si>
+  <si>
+    <t>TP/TP+FP</t>
+  </si>
+  <si>
+    <t>Recall:</t>
+  </si>
+  <si>
+    <t>TP/TP+FN</t>
+  </si>
+  <si>
+    <t>F-Measure:</t>
+  </si>
+  <si>
+    <t>2 * (precision * recall)/(precision+recall)</t>
   </si>
 </sst>
 </file>
@@ -2196,7 +2244,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2376,8 +2424,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2492,6 +2546,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2537,8 +2606,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2894,8 +2966,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G516"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L528"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="27.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -2920,7 +2996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2943,7 +3019,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2957,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -2966,7 +3042,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -2974,10 +3050,10 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -2989,7 +3065,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2997,10 +3073,10 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -3012,7 +3088,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3035,7 +3111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3058,7 +3134,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3081,7 +3157,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -3104,7 +3180,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3112,10 +3188,10 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>7</v>
@@ -3127,7 +3203,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -3135,10 +3211,10 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -3150,7 +3226,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -3158,10 +3234,10 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>8</v>
@@ -3173,7 +3249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -3184,7 +3260,7 @@
         <v>1</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -3196,7 +3272,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -3207,7 +3283,7 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>9</v>
@@ -3219,7 +3295,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -3227,10 +3303,10 @@
         <v>1</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E15">
         <v>9</v>
@@ -3242,7 +3318,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -3250,13 +3326,13 @@
         <v>1</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
       <c r="E16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -3265,7 +3341,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3288,7 +3364,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -3296,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -3311,7 +3387,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -3334,7 +3410,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -3342,10 +3418,10 @@
         <v>1</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -3357,7 +3433,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -3380,7 +3456,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -3403,7 +3479,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -3411,22 +3487,22 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>21</v>
       </c>
       <c r="E23">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -3437,7 +3513,7 @@
         <v>3</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>9</v>
@@ -3449,7 +3525,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -3472,7 +3548,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3483,7 +3559,7 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>4</v>
@@ -3495,7 +3571,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -3503,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -3518,7 +3594,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -3532,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -3541,7 +3617,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -3564,7 +3640,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -3587,7 +3663,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>44</v>
       </c>
@@ -3601,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -3610,7 +3686,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -3624,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
@@ -3633,7 +3709,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -3641,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -3656,7 +3732,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -3664,10 +3740,10 @@
         <v>1</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>7</v>
@@ -3679,7 +3755,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -3687,13 +3763,13 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
@@ -3702,7 +3778,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>51</v>
       </c>
@@ -3710,13 +3786,13 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>5</v>
       </c>
       <c r="E36">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
@@ -3725,7 +3801,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>52</v>
       </c>
@@ -3733,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>10</v>
@@ -3742,13 +3818,13 @@
         <v>42</v>
       </c>
       <c r="F37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>54</v>
       </c>
@@ -3771,7 +3847,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>56</v>
       </c>
@@ -3794,7 +3870,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -3802,13 +3878,13 @@
         <v>0</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
@@ -3817,7 +3893,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>58</v>
       </c>
@@ -3825,7 +3901,7 @@
         <v>1</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -3840,7 +3916,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>60</v>
       </c>
@@ -3848,13 +3924,13 @@
         <v>1</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F42" t="b">
         <v>0</v>
@@ -3863,7 +3939,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -3871,7 +3947,7 @@
         <v>4</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -3886,7 +3962,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>63</v>
       </c>
@@ -3894,10 +3970,10 @@
         <v>1</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -3909,7 +3985,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>65</v>
       </c>
@@ -3917,13 +3993,13 @@
         <v>0</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>2</v>
       </c>
       <c r="E45">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -3932,7 +4008,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>67</v>
       </c>
@@ -3940,7 +4016,7 @@
         <v>1</v>
       </c>
       <c r="C46">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -3955,7 +4031,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>68</v>
       </c>
@@ -3969,7 +4045,7 @@
         <v>34</v>
       </c>
       <c r="E47">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -3978,7 +4054,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>69</v>
       </c>
@@ -4001,7 +4077,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>70</v>
       </c>
@@ -4009,7 +4085,7 @@
         <v>1</v>
       </c>
       <c r="C49">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -4024,15 +4100,15 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>71</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -4047,7 +4123,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>72</v>
       </c>
@@ -4058,7 +4134,7 @@
         <v>2</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>6</v>
@@ -4070,7 +4146,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>74</v>
       </c>
@@ -4093,7 +4169,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>76</v>
       </c>
@@ -4116,7 +4192,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>77</v>
       </c>
@@ -4124,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -4139,7 +4215,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>78</v>
       </c>
@@ -4147,10 +4223,10 @@
         <v>0</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E55">
         <v>13</v>
@@ -4162,7 +4238,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>79</v>
       </c>
@@ -4185,7 +4261,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>81</v>
       </c>
@@ -4193,13 +4269,13 @@
         <v>5</v>
       </c>
       <c r="C57">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>64</v>
       </c>
       <c r="E57">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
@@ -4208,7 +4284,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>82</v>
       </c>
@@ -4216,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="C58">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -4231,7 +4307,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>84</v>
       </c>
@@ -4239,10 +4315,10 @@
         <v>1</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4254,7 +4330,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>86</v>
       </c>
@@ -4277,7 +4353,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>88</v>
       </c>
@@ -4300,7 +4376,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>89</v>
       </c>
@@ -4323,7 +4399,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>90</v>
       </c>
@@ -4346,7 +4422,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>91</v>
       </c>
@@ -4369,7 +4445,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>92</v>
       </c>
@@ -4392,7 +4468,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>93</v>
       </c>
@@ -4415,7 +4491,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>94</v>
       </c>
@@ -4438,7 +4514,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>95</v>
       </c>
@@ -4461,7 +4537,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>96</v>
       </c>
@@ -4484,7 +4560,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>97</v>
       </c>
@@ -4507,7 +4583,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>98</v>
       </c>
@@ -4530,7 +4606,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>99</v>
       </c>
@@ -4553,7 +4629,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>100</v>
       </c>
@@ -4576,7 +4652,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>101</v>
       </c>
@@ -4599,7 +4675,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>102</v>
       </c>
@@ -4622,7 +4698,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>103</v>
       </c>
@@ -4630,22 +4706,22 @@
         <v>0</v>
       </c>
       <c r="C76">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E76">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>104</v>
       </c>
@@ -4668,7 +4744,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>105</v>
       </c>
@@ -4676,7 +4752,7 @@
         <v>1</v>
       </c>
       <c r="C78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -4691,7 +4767,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>106</v>
       </c>
@@ -4714,7 +4790,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>107</v>
       </c>
@@ -4737,7 +4813,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>108</v>
       </c>
@@ -4760,7 +4836,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>109</v>
       </c>
@@ -4783,7 +4859,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>110</v>
       </c>
@@ -4806,7 +4882,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>111</v>
       </c>
@@ -4829,7 +4905,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>112</v>
       </c>
@@ -4852,7 +4928,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>113</v>
       </c>
@@ -4863,7 +4939,7 @@
         <v>4</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86">
         <v>12</v>
@@ -4875,21 +4951,21 @@
         <v>87</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>114</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F87" t="b">
         <v>0</v>
@@ -4898,7 +4974,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>115</v>
       </c>
@@ -4921,7 +4997,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>116</v>
       </c>
@@ -4944,7 +5020,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>117</v>
       </c>
@@ -4952,10 +5028,10 @@
         <v>1</v>
       </c>
       <c r="C90">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90">
         <v>36</v>
@@ -4967,7 +5043,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>118</v>
       </c>
@@ -4975,7 +5051,7 @@
         <v>1</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -4990,7 +5066,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>119</v>
       </c>
@@ -5013,7 +5089,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>120</v>
       </c>
@@ -5036,7 +5112,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>121</v>
       </c>
@@ -5059,7 +5135,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>122</v>
       </c>
@@ -5082,7 +5158,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>123</v>
       </c>
@@ -5105,7 +5181,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>124</v>
       </c>
@@ -5113,7 +5189,7 @@
         <v>1</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -5128,7 +5204,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>125</v>
       </c>
@@ -5151,7 +5227,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>126</v>
       </c>
@@ -5174,7 +5250,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>127</v>
       </c>
@@ -5197,7 +5273,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>128</v>
       </c>
@@ -5220,7 +5296,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>129</v>
       </c>
@@ -5243,7 +5319,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>130</v>
       </c>
@@ -5251,10 +5327,10 @@
         <v>1</v>
       </c>
       <c r="C103">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103">
         <v>20</v>
@@ -5267,14 +5343,14 @@
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
+      <c r="A104" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D104">
         <v>5</v>
@@ -5289,7 +5365,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>132</v>
       </c>
@@ -5312,7 +5388,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>133</v>
       </c>
@@ -5335,7 +5411,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>134</v>
       </c>
@@ -5358,7 +5434,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>135</v>
       </c>
@@ -5381,7 +5457,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>136</v>
       </c>
@@ -5389,7 +5465,7 @@
         <v>1</v>
       </c>
       <c r="C109">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -5404,7 +5480,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>137</v>
       </c>
@@ -5427,7 +5503,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>138</v>
       </c>
@@ -5450,7 +5526,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>139</v>
       </c>
@@ -5473,7 +5549,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>140</v>
       </c>
@@ -5496,7 +5572,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>141</v>
       </c>
@@ -5504,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="C114">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -5519,15 +5595,15 @@
         <v>87</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>142</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D115">
         <v>3</v>
@@ -5542,7 +5618,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>143</v>
       </c>
@@ -5565,7 +5641,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>144</v>
       </c>
@@ -5588,7 +5664,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>145</v>
       </c>
@@ -5602,7 +5678,7 @@
         <v>0</v>
       </c>
       <c r="E118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" t="b">
         <v>0</v>
@@ -5611,7 +5687,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>146</v>
       </c>
@@ -5625,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="E119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" t="b">
         <v>0</v>
@@ -5634,7 +5710,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>147</v>
       </c>
@@ -5657,7 +5733,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>148</v>
       </c>
@@ -5680,7 +5756,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>149</v>
       </c>
@@ -5703,7 +5779,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>150</v>
       </c>
@@ -5711,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="C123">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D123">
         <v>2</v>
@@ -5726,7 +5802,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>151</v>
       </c>
@@ -5734,13 +5810,13 @@
         <v>1</v>
       </c>
       <c r="C124">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D124">
         <v>0</v>
       </c>
       <c r="E124">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F124" t="b">
         <v>0</v>
@@ -5749,7 +5825,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>152</v>
       </c>
@@ -5757,10 +5833,10 @@
         <v>1</v>
       </c>
       <c r="C125">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>11</v>
@@ -5772,7 +5848,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>153</v>
       </c>
@@ -5780,10 +5856,10 @@
         <v>1</v>
       </c>
       <c r="C126">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126">
         <v>9</v>
@@ -5795,7 +5871,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>154</v>
       </c>
@@ -5803,10 +5879,10 @@
         <v>1</v>
       </c>
       <c r="C127">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>26</v>
@@ -5818,7 +5894,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>155</v>
       </c>
@@ -5841,7 +5917,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>156</v>
       </c>
@@ -5864,7 +5940,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>157</v>
       </c>
@@ -5887,21 +5963,21 @@
         <v>87</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>158</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F131" t="b">
         <v>0</v>
@@ -5910,15 +5986,15 @@
         <v>87</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>159</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -5933,7 +6009,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>160</v>
       </c>
@@ -5941,10 +6017,10 @@
         <v>1</v>
       </c>
       <c r="C133">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>16</v>
@@ -5956,7 +6032,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>161</v>
       </c>
@@ -5964,10 +6040,10 @@
         <v>1</v>
       </c>
       <c r="C134">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>15</v>
@@ -5979,7 +6055,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>162</v>
       </c>
@@ -5987,7 +6063,7 @@
         <v>1</v>
       </c>
       <c r="C135">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D135">
         <v>5</v>
@@ -5996,13 +6072,13 @@
         <v>34</v>
       </c>
       <c r="F135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>163</v>
       </c>
@@ -6025,7 +6101,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>164</v>
       </c>
@@ -6048,7 +6124,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>165</v>
       </c>
@@ -6071,7 +6147,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>166</v>
       </c>
@@ -6094,7 +6170,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>167</v>
       </c>
@@ -6117,7 +6193,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>168</v>
       </c>
@@ -6140,7 +6216,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>169</v>
       </c>
@@ -6163,7 +6239,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>170</v>
       </c>
@@ -6186,7 +6262,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>171</v>
       </c>
@@ -6209,7 +6285,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>172</v>
       </c>
@@ -6232,7 +6308,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>173</v>
       </c>
@@ -6240,7 +6316,7 @@
         <v>1</v>
       </c>
       <c r="C146">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -6255,7 +6331,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>174</v>
       </c>
@@ -6263,7 +6339,7 @@
         <v>1</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -6278,7 +6354,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>175</v>
       </c>
@@ -6286,10 +6362,10 @@
         <v>1</v>
       </c>
       <c r="C148">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148">
         <v>29</v>
@@ -6301,18 +6377,18 @@
         <v>176</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>177</v>
       </c>
       <c r="B149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149">
         <v>7</v>
@@ -6324,7 +6400,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>179</v>
       </c>
@@ -6335,7 +6411,7 @@
         <v>3</v>
       </c>
       <c r="D150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150">
         <v>5</v>
@@ -6347,7 +6423,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>181</v>
       </c>
@@ -6370,7 +6446,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>182</v>
       </c>
@@ -6381,7 +6457,7 @@
         <v>3</v>
       </c>
       <c r="D152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152">
         <v>5</v>
@@ -6393,7 +6469,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>183</v>
       </c>
@@ -6401,10 +6477,10 @@
         <v>1</v>
       </c>
       <c r="C153">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D153">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E153">
         <v>6</v>
@@ -6416,7 +6492,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>184</v>
       </c>
@@ -6424,7 +6500,7 @@
         <v>1</v>
       </c>
       <c r="C154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D154">
         <v>1</v>
@@ -6439,7 +6515,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>185</v>
       </c>
@@ -6462,7 +6538,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>187</v>
       </c>
@@ -6470,7 +6546,7 @@
         <v>1</v>
       </c>
       <c r="C156">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -6485,7 +6561,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>188</v>
       </c>
@@ -6493,10 +6569,10 @@
         <v>0</v>
       </c>
       <c r="C157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E157">
         <v>3</v>
@@ -6508,7 +6584,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>189</v>
       </c>
@@ -6516,7 +6592,7 @@
         <v>1</v>
       </c>
       <c r="C158">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D158">
         <v>0</v>
@@ -6531,7 +6607,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>191</v>
       </c>
@@ -6539,7 +6615,7 @@
         <v>7</v>
       </c>
       <c r="C159">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -6554,7 +6630,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>192</v>
       </c>
@@ -6562,13 +6638,13 @@
         <v>0</v>
       </c>
       <c r="C160">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D160">
         <v>1</v>
       </c>
       <c r="E160">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F160" t="b">
         <v>0</v>
@@ -6577,7 +6653,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>193</v>
       </c>
@@ -6585,10 +6661,10 @@
         <v>0</v>
       </c>
       <c r="C161">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D161">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E161">
         <v>51</v>
@@ -6600,7 +6676,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>194</v>
       </c>
@@ -6608,22 +6684,22 @@
         <v>0</v>
       </c>
       <c r="C162">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D162">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E162">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>195</v>
       </c>
@@ -6631,7 +6707,7 @@
         <v>0</v>
       </c>
       <c r="C163">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D163">
         <v>7</v>
@@ -6640,13 +6716,13 @@
         <v>122</v>
       </c>
       <c r="F163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G163" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>196</v>
       </c>
@@ -6654,13 +6730,13 @@
         <v>6</v>
       </c>
       <c r="C164">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D164">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E164">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F164" t="b">
         <v>0</v>
@@ -6669,15 +6745,15 @@
         <v>190</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>197</v>
       </c>
       <c r="B165">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C165">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D165">
         <v>4</v>
@@ -6686,27 +6762,27 @@
         <v>56</v>
       </c>
       <c r="F165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A166" t="s">
+      <c r="A166" s="1" t="s">
         <v>199</v>
       </c>
       <c r="B166">
         <v>1</v>
       </c>
       <c r="C166">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D166">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E166">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F166" t="b">
         <v>1</v>
@@ -6715,7 +6791,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>200</v>
       </c>
@@ -6738,7 +6814,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>202</v>
       </c>
@@ -6761,7 +6837,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>203</v>
       </c>
@@ -6769,7 +6845,7 @@
         <v>1</v>
       </c>
       <c r="C169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D169">
         <v>0</v>
@@ -6784,7 +6860,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>205</v>
       </c>
@@ -6807,7 +6883,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>206</v>
       </c>
@@ -6830,7 +6906,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>207</v>
       </c>
@@ -6853,7 +6929,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>208</v>
       </c>
@@ -6861,7 +6937,7 @@
         <v>1</v>
       </c>
       <c r="C173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -6876,7 +6952,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>209</v>
       </c>
@@ -6899,7 +6975,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>210</v>
       </c>
@@ -6922,7 +6998,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>211</v>
       </c>
@@ -6945,7 +7021,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>213</v>
       </c>
@@ -6953,7 +7029,7 @@
         <v>1</v>
       </c>
       <c r="C177">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -6968,7 +7044,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>215</v>
       </c>
@@ -6976,10 +7052,10 @@
         <v>1</v>
       </c>
       <c r="C178">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D178">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E178">
         <v>3</v>
@@ -6991,7 +7067,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>216</v>
       </c>
@@ -7014,7 +7090,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>217</v>
       </c>
@@ -7037,7 +7113,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>219</v>
       </c>
@@ -7045,10 +7121,10 @@
         <v>1</v>
       </c>
       <c r="C181">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D181">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E181">
         <v>8</v>
@@ -7060,18 +7136,18 @@
         <v>218</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>220</v>
       </c>
       <c r="B182">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C182">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182">
         <v>29</v>
@@ -7083,7 +7159,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>222</v>
       </c>
@@ -7106,7 +7182,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>224</v>
       </c>
@@ -7129,7 +7205,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>226</v>
       </c>
@@ -7152,7 +7228,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>228</v>
       </c>
@@ -7176,17 +7252,17 @@
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A187" t="s">
+      <c r="A187" s="1" t="s">
         <v>230</v>
       </c>
       <c r="B187">
         <v>1</v>
       </c>
       <c r="C187">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D187">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E187">
         <v>148</v>
@@ -7198,7 +7274,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>231</v>
       </c>
@@ -7221,7 +7297,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>233</v>
       </c>
@@ -7229,7 +7305,7 @@
         <v>1</v>
       </c>
       <c r="C189">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -7244,7 +7320,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>235</v>
       </c>
@@ -7252,10 +7328,10 @@
         <v>1</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E190">
         <v>1</v>
@@ -7267,7 +7343,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>237</v>
       </c>
@@ -7275,10 +7351,10 @@
         <v>0</v>
       </c>
       <c r="C191">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D191">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E191">
         <v>23</v>
@@ -7290,7 +7366,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>239</v>
       </c>
@@ -7313,7 +7389,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>241</v>
       </c>
@@ -7336,7 +7412,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>243</v>
       </c>
@@ -7344,22 +7420,22 @@
         <v>1</v>
       </c>
       <c r="C194">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D194">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E194">
         <v>38</v>
       </c>
       <c r="F194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>245</v>
       </c>
@@ -7367,10 +7443,10 @@
         <v>1</v>
       </c>
       <c r="C195">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E195">
         <v>7</v>
@@ -7382,7 +7458,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>247</v>
       </c>
@@ -7390,10 +7466,10 @@
         <v>1</v>
       </c>
       <c r="C196">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D196">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E196">
         <v>6</v>
@@ -7405,7 +7481,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>249</v>
       </c>
@@ -7413,7 +7489,7 @@
         <v>1</v>
       </c>
       <c r="C197">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D197">
         <v>0</v>
@@ -7428,7 +7504,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>251</v>
       </c>
@@ -7436,7 +7512,7 @@
         <v>1</v>
       </c>
       <c r="C198">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -7451,53 +7527,53 @@
         <v>250</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>252</v>
       </c>
       <c r="B199">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C199">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="D199">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E199">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G199" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>254</v>
       </c>
       <c r="B200">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C200">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D200">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E200">
         <v>110</v>
       </c>
       <c r="F200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G200" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>256</v>
       </c>
@@ -7508,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E201">
         <v>2</v>
@@ -7520,7 +7596,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>257</v>
       </c>
@@ -7528,7 +7604,7 @@
         <v>1</v>
       </c>
       <c r="C202">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -7543,7 +7619,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>259</v>
       </c>
@@ -7551,10 +7627,10 @@
         <v>1</v>
       </c>
       <c r="C203">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D203">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E203">
         <v>9</v>
@@ -7566,15 +7642,15 @@
         <v>260</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>261</v>
       </c>
       <c r="B204">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C204">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="D204">
         <v>21</v>
@@ -7583,13 +7659,13 @@
         <v>262</v>
       </c>
       <c r="F204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G204" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>263</v>
       </c>
@@ -7597,10 +7673,10 @@
         <v>1</v>
       </c>
       <c r="C205">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E205">
         <v>9</v>
@@ -7612,18 +7688,18 @@
         <v>264</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>265</v>
       </c>
       <c r="B206">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C206">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D206">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E206">
         <v>14</v>
@@ -7635,7 +7711,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>267</v>
       </c>
@@ -7646,7 +7722,7 @@
         <v>1</v>
       </c>
       <c r="D207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E207">
         <v>4</v>
@@ -7658,7 +7734,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>269</v>
       </c>
@@ -7666,7 +7742,7 @@
         <v>1</v>
       </c>
       <c r="C208">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -7681,41 +7757,41 @@
         <v>270</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>271</v>
       </c>
       <c r="B209">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C209">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="D209">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E209">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G209" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>273</v>
       </c>
       <c r="B210">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C210">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E210">
         <v>4</v>
@@ -7727,18 +7803,18 @@
         <v>274</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>275</v>
       </c>
       <c r="B211">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C211">
+        <v>4</v>
+      </c>
+      <c r="D211">
         <v>3</v>
-      </c>
-      <c r="D211">
-        <v>5</v>
       </c>
       <c r="E211">
         <v>12</v>
@@ -7750,7 +7826,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>277</v>
       </c>
@@ -7758,10 +7834,10 @@
         <v>1</v>
       </c>
       <c r="C212">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E212">
         <v>3</v>
@@ -7773,7 +7849,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>279</v>
       </c>
@@ -7781,10 +7857,10 @@
         <v>1</v>
       </c>
       <c r="C213">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D213">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E213">
         <v>3</v>
@@ -7796,7 +7872,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>281</v>
       </c>
@@ -7819,7 +7895,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>283</v>
       </c>
@@ -7827,7 +7903,7 @@
         <v>0</v>
       </c>
       <c r="C215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -7842,7 +7918,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>285</v>
       </c>
@@ -7865,7 +7941,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>286</v>
       </c>
@@ -7873,13 +7949,13 @@
         <v>0</v>
       </c>
       <c r="C217">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D217">
         <v>3</v>
       </c>
       <c r="E217">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F217" t="b">
         <v>0</v>
@@ -7888,7 +7964,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>287</v>
       </c>
@@ -7896,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="C218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D218">
         <v>4</v>
@@ -7911,7 +7987,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>288</v>
       </c>
@@ -7919,7 +7995,7 @@
         <v>0</v>
       </c>
       <c r="C219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D219">
         <v>0</v>
@@ -7934,7 +8010,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>289</v>
       </c>
@@ -7957,7 +8033,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>290</v>
       </c>
@@ -7965,7 +8041,7 @@
         <v>0</v>
       </c>
       <c r="C221">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D221">
         <v>3</v>
@@ -7980,7 +8056,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>292</v>
       </c>
@@ -7988,22 +8064,22 @@
         <v>1</v>
       </c>
       <c r="C222">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D222">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E222">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F222" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G222" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>293</v>
       </c>
@@ -8011,22 +8087,22 @@
         <v>1</v>
       </c>
       <c r="C223">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D223">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E223">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F223" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G223" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>294</v>
       </c>
@@ -8049,21 +8125,21 @@
         <v>295</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>296</v>
       </c>
       <c r="B225">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C225">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D225">
         <v>0</v>
       </c>
       <c r="E225">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F225" t="b">
         <v>0</v>
@@ -8072,7 +8148,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>298</v>
       </c>
@@ -8080,7 +8156,7 @@
         <v>0</v>
       </c>
       <c r="C226">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D226">
         <v>0</v>
@@ -8095,7 +8171,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>300</v>
       </c>
@@ -8103,13 +8179,13 @@
         <v>0</v>
       </c>
       <c r="C227">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D227">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E227">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F227" t="b">
         <v>0</v>
@@ -8118,7 +8194,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>301</v>
       </c>
@@ -8126,7 +8202,7 @@
         <v>0</v>
       </c>
       <c r="C228">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D228">
         <v>0</v>
@@ -8141,7 +8217,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>302</v>
       </c>
@@ -8149,13 +8225,13 @@
         <v>1</v>
       </c>
       <c r="C229">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D229">
         <v>1</v>
       </c>
       <c r="E229">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F229" t="b">
         <v>0</v>
@@ -8164,7 +8240,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>304</v>
       </c>
@@ -8172,7 +8248,7 @@
         <v>1</v>
       </c>
       <c r="C230">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D230">
         <v>1</v>
@@ -8187,7 +8263,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>306</v>
       </c>
@@ -8195,10 +8271,10 @@
         <v>0</v>
       </c>
       <c r="C231">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E231">
         <v>12</v>
@@ -8210,7 +8286,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>308</v>
       </c>
@@ -8233,7 +8309,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>310</v>
       </c>
@@ -8256,7 +8332,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>312</v>
       </c>
@@ -8279,7 +8355,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>313</v>
       </c>
@@ -8302,7 +8378,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>315</v>
       </c>
@@ -8316,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="E236">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F236" t="b">
         <v>0</v>
@@ -8325,7 +8401,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>316</v>
       </c>
@@ -8339,7 +8415,7 @@
         <v>0</v>
       </c>
       <c r="E237">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F237" t="b">
         <v>0</v>
@@ -8348,7 +8424,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>317</v>
       </c>
@@ -8362,7 +8438,7 @@
         <v>0</v>
       </c>
       <c r="E238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F238" t="b">
         <v>0</v>
@@ -8371,7 +8447,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>318</v>
       </c>
@@ -8385,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="E239">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F239" t="b">
         <v>0</v>
@@ -8394,7 +8470,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>319</v>
       </c>
@@ -8408,7 +8484,7 @@
         <v>0</v>
       </c>
       <c r="E240">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F240" t="b">
         <v>0</v>
@@ -8417,7 +8493,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>320</v>
       </c>
@@ -8440,7 +8516,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>321</v>
       </c>
@@ -8454,7 +8530,7 @@
         <v>0</v>
       </c>
       <c r="E242">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F242" t="b">
         <v>0</v>
@@ -8463,7 +8539,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>322</v>
       </c>
@@ -8471,7 +8547,7 @@
         <v>1</v>
       </c>
       <c r="C243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D243">
         <v>0</v>
@@ -8486,7 +8562,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>323</v>
       </c>
@@ -8494,10 +8570,10 @@
         <v>1</v>
       </c>
       <c r="C244">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E244">
         <v>2</v>
@@ -8509,7 +8585,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>325</v>
       </c>
@@ -8517,7 +8593,7 @@
         <v>0</v>
       </c>
       <c r="C245">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D245">
         <v>1</v>
@@ -8532,7 +8608,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>327</v>
       </c>
@@ -8555,7 +8631,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>328</v>
       </c>
@@ -8578,7 +8654,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>329</v>
       </c>
@@ -8586,13 +8662,13 @@
         <v>0</v>
       </c>
       <c r="C248">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D248">
         <v>0</v>
       </c>
       <c r="E248">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F248" t="b">
         <v>0</v>
@@ -8601,7 +8677,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>330</v>
       </c>
@@ -8609,7 +8685,7 @@
         <v>0</v>
       </c>
       <c r="C249">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D249">
         <v>3</v>
@@ -8624,7 +8700,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>331</v>
       </c>
@@ -8632,13 +8708,13 @@
         <v>1</v>
       </c>
       <c r="C250">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D250">
         <v>1</v>
       </c>
       <c r="E250">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F250" t="b">
         <v>0</v>
@@ -8647,7 +8723,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>332</v>
       </c>
@@ -8655,7 +8731,7 @@
         <v>1</v>
       </c>
       <c r="C251">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D251">
         <v>0</v>
@@ -8670,7 +8746,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>333</v>
       </c>
@@ -8678,7 +8754,7 @@
         <v>0</v>
       </c>
       <c r="C252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D252">
         <v>1</v>
@@ -8693,7 +8769,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>334</v>
       </c>
@@ -8701,13 +8777,13 @@
         <v>0</v>
       </c>
       <c r="C253">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D253">
         <v>0</v>
       </c>
       <c r="E253">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F253" t="b">
         <v>0</v>
@@ -8716,7 +8792,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>335</v>
       </c>
@@ -8724,7 +8800,7 @@
         <v>0</v>
       </c>
       <c r="C254">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D254">
         <v>0</v>
@@ -8739,7 +8815,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>337</v>
       </c>
@@ -8762,7 +8838,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>339</v>
       </c>
@@ -8785,7 +8861,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>340</v>
       </c>
@@ -8793,13 +8869,13 @@
         <v>0</v>
       </c>
       <c r="C257">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D257">
         <v>2</v>
       </c>
       <c r="E257">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F257" t="b">
         <v>0</v>
@@ -8808,7 +8884,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>341</v>
       </c>
@@ -8831,7 +8907,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>342</v>
       </c>
@@ -8854,7 +8930,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>343</v>
       </c>
@@ -8877,7 +8953,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>344</v>
       </c>
@@ -8900,7 +8976,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>345</v>
       </c>
@@ -8923,7 +8999,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>346</v>
       </c>
@@ -8946,7 +9022,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>348</v>
       </c>
@@ -8969,7 +9045,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>349</v>
       </c>
@@ -8992,7 +9068,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>350</v>
       </c>
@@ -9000,7 +9076,7 @@
         <v>0</v>
       </c>
       <c r="C266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D266">
         <v>0</v>
@@ -9015,7 +9091,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>351</v>
       </c>
@@ -9038,7 +9114,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>353</v>
       </c>
@@ -9061,7 +9137,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>355</v>
       </c>
@@ -9069,10 +9145,10 @@
         <v>1</v>
       </c>
       <c r="C269">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D269">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E269">
         <v>2</v>
@@ -9084,7 +9160,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>357</v>
       </c>
@@ -9092,10 +9168,10 @@
         <v>1</v>
       </c>
       <c r="C270">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D270">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E270">
         <v>3</v>
@@ -9107,7 +9183,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>358</v>
       </c>
@@ -9118,10 +9194,10 @@
         <v>0</v>
       </c>
       <c r="D271">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E271">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F271" t="b">
         <v>0</v>
@@ -9130,7 +9206,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>359</v>
       </c>
@@ -9138,10 +9214,10 @@
         <v>1</v>
       </c>
       <c r="C272">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D272">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E272">
         <v>13</v>
@@ -9153,7 +9229,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>360</v>
       </c>
@@ -9161,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="C273">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D273">
         <v>0</v>
@@ -9176,7 +9252,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>362</v>
       </c>
@@ -9184,10 +9260,10 @@
         <v>1</v>
       </c>
       <c r="C274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D274">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E274">
         <v>1</v>
@@ -9199,7 +9275,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>363</v>
       </c>
@@ -9207,13 +9283,13 @@
         <v>0</v>
       </c>
       <c r="C275">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D275">
         <v>6</v>
       </c>
       <c r="E275">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F275" t="b">
         <v>0</v>
@@ -9222,7 +9298,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>364</v>
       </c>
@@ -9230,10 +9306,10 @@
         <v>1</v>
       </c>
       <c r="C276">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D276">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E276">
         <v>9</v>
@@ -9245,7 +9321,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>365</v>
       </c>
@@ -9268,7 +9344,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>366</v>
       </c>
@@ -9291,7 +9367,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>368</v>
       </c>
@@ -9314,7 +9390,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>369</v>
       </c>
@@ -9322,7 +9398,7 @@
         <v>0</v>
       </c>
       <c r="C280">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D280">
         <v>1</v>
@@ -9337,7 +9413,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>371</v>
       </c>
@@ -9345,7 +9421,7 @@
         <v>1</v>
       </c>
       <c r="C281">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D281">
         <v>0</v>
@@ -9360,7 +9436,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>372</v>
       </c>
@@ -9368,7 +9444,7 @@
         <v>1</v>
       </c>
       <c r="C282">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D282">
         <v>0</v>
@@ -9383,7 +9459,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>373</v>
       </c>
@@ -9391,7 +9467,7 @@
         <v>1</v>
       </c>
       <c r="C283">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D283">
         <v>0</v>
@@ -9406,7 +9482,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>374</v>
       </c>
@@ -9414,7 +9490,7 @@
         <v>1</v>
       </c>
       <c r="C284">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D284">
         <v>0</v>
@@ -9429,7 +9505,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>375</v>
       </c>
@@ -9437,13 +9513,13 @@
         <v>1</v>
       </c>
       <c r="C285">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D285">
         <v>0</v>
       </c>
       <c r="E285">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F285" t="b">
         <v>0</v>
@@ -9452,7 +9528,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>376</v>
       </c>
@@ -9460,10 +9536,10 @@
         <v>1</v>
       </c>
       <c r="C286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E286">
         <v>1</v>
@@ -9475,7 +9551,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>377</v>
       </c>
@@ -9498,7 +9574,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>379</v>
       </c>
@@ -9521,7 +9597,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>380</v>
       </c>
@@ -9544,7 +9620,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>381</v>
       </c>
@@ -9552,7 +9628,7 @@
         <v>0</v>
       </c>
       <c r="C290">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D290">
         <v>0</v>
@@ -9567,7 +9643,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>382</v>
       </c>
@@ -9575,7 +9651,7 @@
         <v>0</v>
       </c>
       <c r="C291">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D291">
         <v>0</v>
@@ -9590,7 +9666,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>383</v>
       </c>
@@ -9598,7 +9674,7 @@
         <v>0</v>
       </c>
       <c r="C292">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D292">
         <v>0</v>
@@ -9613,7 +9689,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>384</v>
       </c>
@@ -9621,7 +9697,7 @@
         <v>0</v>
       </c>
       <c r="C293">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D293">
         <v>0</v>
@@ -9636,7 +9712,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>385</v>
       </c>
@@ -9644,7 +9720,7 @@
         <v>0</v>
       </c>
       <c r="C294">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D294">
         <v>0</v>
@@ -9659,7 +9735,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>386</v>
       </c>
@@ -9682,7 +9758,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>387</v>
       </c>
@@ -9690,13 +9766,13 @@
         <v>1</v>
       </c>
       <c r="C296">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D296">
         <v>0</v>
       </c>
       <c r="E296">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F296" t="b">
         <v>0</v>
@@ -9705,7 +9781,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>388</v>
       </c>
@@ -9713,22 +9789,22 @@
         <v>1</v>
       </c>
       <c r="C297">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D297">
         <v>4</v>
       </c>
       <c r="E297">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F297" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G297" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>389</v>
       </c>
@@ -9736,13 +9812,13 @@
         <v>1</v>
       </c>
       <c r="C298">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D298">
         <v>0</v>
       </c>
       <c r="E298">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F298" t="b">
         <v>0</v>
@@ -9751,7 +9827,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>390</v>
       </c>
@@ -9774,7 +9850,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>391</v>
       </c>
@@ -9788,7 +9864,7 @@
         <v>2</v>
       </c>
       <c r="E300">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F300" t="b">
         <v>0</v>
@@ -9798,20 +9874,20 @@
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A301" t="s">
+      <c r="A301" s="1" t="s">
         <v>392</v>
       </c>
       <c r="B301">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C301">
+        <v>24</v>
+      </c>
+      <c r="D301">
         <v>99</v>
       </c>
-      <c r="D301">
-        <v>93</v>
-      </c>
       <c r="E301">
-        <v>526</v>
+        <v>569</v>
       </c>
       <c r="F301" t="b">
         <v>1</v>
@@ -9820,7 +9896,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>393</v>
       </c>
@@ -9828,13 +9904,13 @@
         <v>1</v>
       </c>
       <c r="C302">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D302">
         <v>2</v>
       </c>
       <c r="E302">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F302" t="b">
         <v>0</v>
@@ -9844,20 +9920,20 @@
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A303" t="s">
+      <c r="A303" s="1" t="s">
         <v>394</v>
       </c>
       <c r="B303">
         <v>1</v>
       </c>
       <c r="C303">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D303">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E303">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F303" t="b">
         <v>1</v>
@@ -9866,7 +9942,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>395</v>
       </c>
@@ -9874,22 +9950,22 @@
         <v>1</v>
       </c>
       <c r="C304">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D304">
         <v>4</v>
       </c>
       <c r="E304">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F304" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G304" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>396</v>
       </c>
@@ -9897,7 +9973,7 @@
         <v>0</v>
       </c>
       <c r="C305">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D305">
         <v>1</v>
@@ -9912,7 +9988,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>397</v>
       </c>
@@ -9920,13 +9996,13 @@
         <v>0</v>
       </c>
       <c r="C306">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D306">
         <v>3</v>
       </c>
       <c r="E306">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F306" t="b">
         <v>0</v>
@@ -9935,7 +10011,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>398</v>
       </c>
@@ -9943,36 +10019,36 @@
         <v>0</v>
       </c>
       <c r="C307">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="D307">
         <v>28</v>
       </c>
       <c r="E307">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F307" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G307" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A308" t="s">
+      <c r="A308" s="1" t="s">
         <v>400</v>
       </c>
       <c r="B308">
         <v>1</v>
       </c>
       <c r="C308">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D308">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E308">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F308" t="b">
         <v>1</v>
@@ -9981,7 +10057,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>402</v>
       </c>
@@ -10004,7 +10080,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>404</v>
       </c>
@@ -10027,7 +10103,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>405</v>
       </c>
@@ -10050,7 +10126,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>406</v>
       </c>
@@ -10073,7 +10149,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>407</v>
       </c>
@@ -10096,7 +10172,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>408</v>
       </c>
@@ -10119,7 +10195,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>409</v>
       </c>
@@ -10142,7 +10218,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>410</v>
       </c>
@@ -10165,7 +10241,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>411</v>
       </c>
@@ -10188,7 +10264,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>412</v>
       </c>
@@ -10211,7 +10287,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>413</v>
       </c>
@@ -10234,7 +10310,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>414</v>
       </c>
@@ -10257,7 +10333,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>415</v>
       </c>
@@ -10280,7 +10356,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>416</v>
       </c>
@@ -10303,7 +10379,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>417</v>
       </c>
@@ -10326,7 +10402,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>418</v>
       </c>
@@ -10349,7 +10425,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>419</v>
       </c>
@@ -10372,7 +10448,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>420</v>
       </c>
@@ -10395,7 +10471,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>421</v>
       </c>
@@ -10418,7 +10494,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>422</v>
       </c>
@@ -10441,7 +10517,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>423</v>
       </c>
@@ -10464,7 +10540,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>424</v>
       </c>
@@ -10487,7 +10563,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>425</v>
       </c>
@@ -10495,13 +10571,13 @@
         <v>0</v>
       </c>
       <c r="C331">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D331">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E331">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F331" t="b">
         <v>0</v>
@@ -10510,7 +10586,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>427</v>
       </c>
@@ -10518,13 +10594,13 @@
         <v>0</v>
       </c>
       <c r="C332">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D332">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E332">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F332" t="b">
         <v>0</v>
@@ -10533,7 +10609,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>429</v>
       </c>
@@ -10556,7 +10632,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>430</v>
       </c>
@@ -10579,7 +10655,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>431</v>
       </c>
@@ -10602,7 +10678,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>432</v>
       </c>
@@ -10625,7 +10701,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>433</v>
       </c>
@@ -10648,7 +10724,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>434</v>
       </c>
@@ -10671,7 +10747,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>435</v>
       </c>
@@ -10694,7 +10770,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>436</v>
       </c>
@@ -10717,7 +10793,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>437</v>
       </c>
@@ -10740,7 +10816,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>439</v>
       </c>
@@ -10763,7 +10839,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>440</v>
       </c>
@@ -10786,7 +10862,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>441</v>
       </c>
@@ -10809,7 +10885,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>443</v>
       </c>
@@ -10832,7 +10908,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>445</v>
       </c>
@@ -10855,7 +10931,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>447</v>
       </c>
@@ -10878,7 +10954,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>448</v>
       </c>
@@ -10901,7 +10977,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>450</v>
       </c>
@@ -10924,7 +11000,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>451</v>
       </c>
@@ -10947,7 +11023,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>452</v>
       </c>
@@ -10955,7 +11031,7 @@
         <v>0</v>
       </c>
       <c r="C351">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D351">
         <v>0</v>
@@ -10970,7 +11046,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>454</v>
       </c>
@@ -10993,7 +11069,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>456</v>
       </c>
@@ -11001,7 +11077,7 @@
         <v>0</v>
       </c>
       <c r="C353">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D353">
         <v>0</v>
@@ -11016,7 +11092,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>458</v>
       </c>
@@ -11039,7 +11115,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>460</v>
       </c>
@@ -11062,7 +11138,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>462</v>
       </c>
@@ -11085,7 +11161,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>464</v>
       </c>
@@ -11108,7 +11184,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>465</v>
       </c>
@@ -11131,7 +11207,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>466</v>
       </c>
@@ -11154,7 +11230,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>468</v>
       </c>
@@ -11177,7 +11253,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>470</v>
       </c>
@@ -11200,7 +11276,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>471</v>
       </c>
@@ -11223,7 +11299,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>473</v>
       </c>
@@ -11237,7 +11313,7 @@
         <v>0</v>
       </c>
       <c r="E363">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F363" t="b">
         <v>0</v>
@@ -11246,7 +11322,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>474</v>
       </c>
@@ -11254,7 +11330,7 @@
         <v>0</v>
       </c>
       <c r="C364">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D364">
         <v>0</v>
@@ -11269,7 +11345,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>476</v>
       </c>
@@ -11292,7 +11368,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>478</v>
       </c>
@@ -11300,7 +11376,7 @@
         <v>11</v>
       </c>
       <c r="C366">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D366">
         <v>6</v>
@@ -11315,30 +11391,30 @@
         <v>479</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>480</v>
       </c>
       <c r="B367">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C367">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D367">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E367">
         <v>28</v>
       </c>
       <c r="F367" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G367" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>482</v>
       </c>
@@ -11346,10 +11422,10 @@
         <v>1</v>
       </c>
       <c r="C368">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D368">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E368">
         <v>6</v>
@@ -11361,7 +11437,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>483</v>
       </c>
@@ -11369,10 +11445,10 @@
         <v>1</v>
       </c>
       <c r="C369">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D369">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E369">
         <v>1</v>
@@ -11384,7 +11460,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>484</v>
       </c>
@@ -11392,22 +11468,22 @@
         <v>1</v>
       </c>
       <c r="C370">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D370">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E370">
         <v>19</v>
       </c>
       <c r="F370" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G370" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>485</v>
       </c>
@@ -11430,7 +11506,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>486</v>
       </c>
@@ -11438,7 +11514,7 @@
         <v>1</v>
       </c>
       <c r="C372">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D372">
         <v>0</v>
@@ -11453,15 +11529,15 @@
         <v>481</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>487</v>
       </c>
       <c r="B373">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C373">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D373">
         <v>0</v>
@@ -11476,7 +11552,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>488</v>
       </c>
@@ -11484,7 +11560,7 @@
         <v>1</v>
       </c>
       <c r="C374">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D374">
         <v>0</v>
@@ -11499,7 +11575,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>489</v>
       </c>
@@ -11522,7 +11598,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>491</v>
       </c>
@@ -11545,7 +11621,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>492</v>
       </c>
@@ -11568,7 +11644,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>493</v>
       </c>
@@ -11582,7 +11658,7 @@
         <v>0</v>
       </c>
       <c r="E378">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F378" t="b">
         <v>0</v>
@@ -11591,7 +11667,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>494</v>
       </c>
@@ -11599,7 +11675,7 @@
         <v>0</v>
       </c>
       <c r="C379">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D379">
         <v>5</v>
@@ -11608,13 +11684,13 @@
         <v>41</v>
       </c>
       <c r="F379" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G379" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>495</v>
       </c>
@@ -11622,7 +11698,7 @@
         <v>1</v>
       </c>
       <c r="C380">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D380">
         <v>0</v>
@@ -11637,7 +11713,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>497</v>
       </c>
@@ -11645,10 +11721,10 @@
         <v>0</v>
       </c>
       <c r="C381">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D381">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E381">
         <v>44</v>
@@ -11660,7 +11736,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>498</v>
       </c>
@@ -11668,7 +11744,7 @@
         <v>0</v>
       </c>
       <c r="C382">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D382">
         <v>1</v>
@@ -11683,7 +11759,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>500</v>
       </c>
@@ -11691,13 +11767,13 @@
         <v>0</v>
       </c>
       <c r="C383">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D383">
         <v>1</v>
       </c>
       <c r="E383">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F383" t="b">
         <v>0</v>
@@ -11706,7 +11782,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>501</v>
       </c>
@@ -11729,7 +11805,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>502</v>
       </c>
@@ -11752,7 +11828,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>503</v>
       </c>
@@ -11775,7 +11851,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>504</v>
       </c>
@@ -11783,22 +11859,22 @@
         <v>0</v>
       </c>
       <c r="C387">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D387">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E387">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F387" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G387" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>505</v>
       </c>
@@ -11821,7 +11897,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>507</v>
       </c>
@@ -11829,22 +11905,22 @@
         <v>0</v>
       </c>
       <c r="C389">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D389">
         <v>8</v>
       </c>
       <c r="E389">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F389" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G389" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>509</v>
       </c>
@@ -11852,22 +11928,22 @@
         <v>0</v>
       </c>
       <c r="C390">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D390">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E390">
         <v>114</v>
       </c>
       <c r="F390" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G390" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>511</v>
       </c>
@@ -11875,7 +11951,7 @@
         <v>0</v>
       </c>
       <c r="C391">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D391">
         <v>0</v>
@@ -11890,7 +11966,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>513</v>
       </c>
@@ -11904,7 +11980,7 @@
         <v>0</v>
       </c>
       <c r="E392">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F392" t="b">
         <v>0</v>
@@ -11913,7 +11989,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>514</v>
       </c>
@@ -11927,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="E393">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F393" t="b">
         <v>0</v>
@@ -11936,7 +12012,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>515</v>
       </c>
@@ -11944,7 +12020,7 @@
         <v>0</v>
       </c>
       <c r="C394">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D394">
         <v>0</v>
@@ -11959,7 +12035,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>516</v>
       </c>
@@ -11967,10 +12043,10 @@
         <v>1</v>
       </c>
       <c r="C395">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D395">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E395">
         <v>1</v>
@@ -11982,7 +12058,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>517</v>
       </c>
@@ -11990,10 +12066,10 @@
         <v>1</v>
       </c>
       <c r="C396">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D396">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E396">
         <v>1</v>
@@ -12005,7 +12081,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>518</v>
       </c>
@@ -12013,7 +12089,7 @@
         <v>0</v>
       </c>
       <c r="C397">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D397">
         <v>0</v>
@@ -12028,7 +12104,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>519</v>
       </c>
@@ -12036,7 +12112,7 @@
         <v>0</v>
       </c>
       <c r="C398">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D398">
         <v>0</v>
@@ -12051,7 +12127,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>520</v>
       </c>
@@ -12074,7 +12150,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>521</v>
       </c>
@@ -12082,13 +12158,13 @@
         <v>0</v>
       </c>
       <c r="C400">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D400">
         <v>2</v>
       </c>
       <c r="E400">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F400" t="b">
         <v>0</v>
@@ -12097,7 +12173,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>523</v>
       </c>
@@ -12105,7 +12181,7 @@
         <v>1</v>
       </c>
       <c r="C401">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D401">
         <v>0</v>
@@ -12120,7 +12196,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>524</v>
       </c>
@@ -12128,10 +12204,10 @@
         <v>0</v>
       </c>
       <c r="C402">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D402">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E402">
         <v>10</v>
@@ -12143,7 +12219,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>525</v>
       </c>
@@ -12166,7 +12242,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>527</v>
       </c>
@@ -12174,13 +12250,13 @@
         <v>0</v>
       </c>
       <c r="C404">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D404">
         <v>0</v>
       </c>
       <c r="E404">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F404" t="b">
         <v>0</v>
@@ -12189,7 +12265,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>529</v>
       </c>
@@ -12197,7 +12273,7 @@
         <v>0</v>
       </c>
       <c r="C405">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D405">
         <v>0</v>
@@ -12212,7 +12288,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>531</v>
       </c>
@@ -12220,10 +12296,10 @@
         <v>0</v>
       </c>
       <c r="C406">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D406">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E406">
         <v>69</v>
@@ -12235,7 +12311,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>533</v>
       </c>
@@ -12258,7 +12334,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>535</v>
       </c>
@@ -12266,13 +12342,13 @@
         <v>0</v>
       </c>
       <c r="C408">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D408">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E408">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="F408" t="b">
         <v>0</v>
@@ -12281,7 +12357,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>537</v>
       </c>
@@ -12304,7 +12380,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>539</v>
       </c>
@@ -12312,7 +12388,7 @@
         <v>9</v>
       </c>
       <c r="C410">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D410">
         <v>26</v>
@@ -12328,52 +12404,52 @@
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A411" t="s">
+      <c r="A411" s="1" t="s">
         <v>540</v>
       </c>
       <c r="B411">
         <v>1</v>
       </c>
       <c r="C411">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D411">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E411">
         <v>16</v>
       </c>
       <c r="F411" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G411" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>541</v>
       </c>
       <c r="B412">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C412">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D412">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E412">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F412" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G412" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>543</v>
       </c>
@@ -12397,20 +12473,20 @@
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A414" t="s">
+      <c r="A414" s="1" t="s">
         <v>545</v>
       </c>
       <c r="B414">
         <v>1</v>
       </c>
       <c r="C414">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="D414">
         <v>25</v>
       </c>
       <c r="E414">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F414" t="b">
         <v>1</v>
@@ -12419,7 +12495,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>547</v>
       </c>
@@ -12442,7 +12518,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>549</v>
       </c>
@@ -12450,7 +12526,7 @@
         <v>1</v>
       </c>
       <c r="C416">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D416">
         <v>0</v>
@@ -12465,7 +12541,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>551</v>
       </c>
@@ -12488,7 +12564,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>553</v>
       </c>
@@ -12511,7 +12587,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>555</v>
       </c>
@@ -12534,7 +12610,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>557</v>
       </c>
@@ -12542,7 +12618,7 @@
         <v>1</v>
       </c>
       <c r="C420">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D420">
         <v>0</v>
@@ -12557,7 +12633,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>559</v>
       </c>
@@ -12565,7 +12641,7 @@
         <v>1</v>
       </c>
       <c r="C421">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D421">
         <v>0</v>
@@ -12580,7 +12656,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>560</v>
       </c>
@@ -12588,7 +12664,7 @@
         <v>1</v>
       </c>
       <c r="C422">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D422">
         <v>0</v>
@@ -12603,7 +12679,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>561</v>
       </c>
@@ -12611,7 +12687,7 @@
         <v>1</v>
       </c>
       <c r="C423">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D423">
         <v>0</v>
@@ -12626,7 +12702,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>562</v>
       </c>
@@ -12634,7 +12710,7 @@
         <v>1</v>
       </c>
       <c r="C424">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D424">
         <v>0</v>
@@ -12649,7 +12725,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>563</v>
       </c>
@@ -12657,7 +12733,7 @@
         <v>1</v>
       </c>
       <c r="C425">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D425">
         <v>0</v>
@@ -12672,7 +12748,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>564</v>
       </c>
@@ -12680,7 +12756,7 @@
         <v>1</v>
       </c>
       <c r="C426">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D426">
         <v>4</v>
@@ -12689,13 +12765,13 @@
         <v>12</v>
       </c>
       <c r="F426" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G426" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>565</v>
       </c>
@@ -12703,13 +12779,13 @@
         <v>1</v>
       </c>
       <c r="C427">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D427">
         <v>1</v>
       </c>
       <c r="E427">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F427" t="b">
         <v>0</v>
@@ -12718,7 +12794,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>566</v>
       </c>
@@ -12726,7 +12802,7 @@
         <v>1</v>
       </c>
       <c r="C428">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D428">
         <v>0</v>
@@ -12741,7 +12817,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>568</v>
       </c>
@@ -12749,7 +12825,7 @@
         <v>1</v>
       </c>
       <c r="C429">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D429">
         <v>0</v>
@@ -12764,7 +12840,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>570</v>
       </c>
@@ -12772,7 +12848,7 @@
         <v>1</v>
       </c>
       <c r="C430">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D430">
         <v>1</v>
@@ -12787,7 +12863,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>571</v>
       </c>
@@ -12810,7 +12886,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>573</v>
       </c>
@@ -12818,7 +12894,7 @@
         <v>1</v>
       </c>
       <c r="C432">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D432">
         <v>0</v>
@@ -12833,7 +12909,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>574</v>
       </c>
@@ -12841,7 +12917,7 @@
         <v>1</v>
       </c>
       <c r="C433">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D433">
         <v>0</v>
@@ -12856,7 +12932,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>576</v>
       </c>
@@ -12864,13 +12940,13 @@
         <v>1</v>
       </c>
       <c r="C434">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D434">
         <v>0</v>
       </c>
       <c r="E434">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F434" t="b">
         <v>0</v>
@@ -12879,7 +12955,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>577</v>
       </c>
@@ -12887,7 +12963,7 @@
         <v>1</v>
       </c>
       <c r="C435">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D435">
         <v>0</v>
@@ -12902,7 +12978,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>578</v>
       </c>
@@ -12910,7 +12986,7 @@
         <v>1</v>
       </c>
       <c r="C436">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D436">
         <v>0</v>
@@ -12925,7 +13001,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>579</v>
       </c>
@@ -12933,7 +13009,7 @@
         <v>1</v>
       </c>
       <c r="C437">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D437">
         <v>0</v>
@@ -12948,7 +13024,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>580</v>
       </c>
@@ -12956,7 +13032,7 @@
         <v>1</v>
       </c>
       <c r="C438">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D438">
         <v>0</v>
@@ -12971,7 +13047,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>581</v>
       </c>
@@ -12979,10 +13055,10 @@
         <v>0</v>
       </c>
       <c r="C439">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D439">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E439">
         <v>19</v>
@@ -12994,7 +13070,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>582</v>
       </c>
@@ -13002,7 +13078,7 @@
         <v>1</v>
       </c>
       <c r="C440">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D440">
         <v>0</v>
@@ -13017,7 +13093,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>583</v>
       </c>
@@ -13025,7 +13101,7 @@
         <v>1</v>
       </c>
       <c r="C441">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D441">
         <v>0</v>
@@ -13040,7 +13116,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>584</v>
       </c>
@@ -13048,7 +13124,7 @@
         <v>1</v>
       </c>
       <c r="C442">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D442">
         <v>0</v>
@@ -13063,7 +13139,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>585</v>
       </c>
@@ -13071,7 +13147,7 @@
         <v>1</v>
       </c>
       <c r="C443">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D443">
         <v>0</v>
@@ -13086,7 +13162,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>587</v>
       </c>
@@ -13094,7 +13170,7 @@
         <v>1</v>
       </c>
       <c r="C444">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D444">
         <v>0</v>
@@ -13109,7 +13185,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>588</v>
       </c>
@@ -13117,13 +13193,13 @@
         <v>1</v>
       </c>
       <c r="C445">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D445">
         <v>0</v>
       </c>
       <c r="E445">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F445" t="b">
         <v>0</v>
@@ -13132,7 +13208,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>590</v>
       </c>
@@ -13140,7 +13216,7 @@
         <v>1</v>
       </c>
       <c r="C446">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D446">
         <v>0</v>
@@ -13155,7 +13231,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>591</v>
       </c>
@@ -13163,7 +13239,7 @@
         <v>1</v>
       </c>
       <c r="C447">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D447">
         <v>0</v>
@@ -13178,7 +13254,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>592</v>
       </c>
@@ -13186,13 +13262,13 @@
         <v>1</v>
       </c>
       <c r="C448">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D448">
         <v>0</v>
       </c>
       <c r="E448">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F448" t="b">
         <v>0</v>
@@ -13201,7 +13277,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>593</v>
       </c>
@@ -13224,7 +13300,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>595</v>
       </c>
@@ -13232,7 +13308,7 @@
         <v>1</v>
       </c>
       <c r="C450">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D450">
         <v>0</v>
@@ -13247,7 +13323,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>596</v>
       </c>
@@ -13255,7 +13331,7 @@
         <v>1</v>
       </c>
       <c r="C451">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D451">
         <v>0</v>
@@ -13270,15 +13346,15 @@
         <v>594</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>597</v>
       </c>
       <c r="B452">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C452">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D452">
         <v>0</v>
@@ -13293,7 +13369,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>598</v>
       </c>
@@ -13301,7 +13377,7 @@
         <v>1</v>
       </c>
       <c r="C453">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D453">
         <v>0</v>
@@ -13316,7 +13392,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>599</v>
       </c>
@@ -13324,7 +13400,7 @@
         <v>1</v>
       </c>
       <c r="C454">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D454">
         <v>0</v>
@@ -13339,7 +13415,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>600</v>
       </c>
@@ -13347,7 +13423,7 @@
         <v>1</v>
       </c>
       <c r="C455">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D455">
         <v>0</v>
@@ -13362,7 +13438,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>601</v>
       </c>
@@ -13370,7 +13446,7 @@
         <v>1</v>
       </c>
       <c r="C456">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D456">
         <v>0</v>
@@ -13385,7 +13461,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>602</v>
       </c>
@@ -13408,7 +13484,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>604</v>
       </c>
@@ -13416,13 +13492,13 @@
         <v>1</v>
       </c>
       <c r="C458">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D458">
         <v>0</v>
       </c>
       <c r="E458">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F458" t="b">
         <v>0</v>
@@ -13431,7 +13507,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>606</v>
       </c>
@@ -13439,7 +13515,7 @@
         <v>1</v>
       </c>
       <c r="C459">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D459">
         <v>0</v>
@@ -13454,7 +13530,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>608</v>
       </c>
@@ -13462,7 +13538,7 @@
         <v>1</v>
       </c>
       <c r="C460">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D460">
         <v>0</v>
@@ -13477,7 +13553,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>610</v>
       </c>
@@ -13485,13 +13561,13 @@
         <v>1</v>
       </c>
       <c r="C461">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D461">
         <v>0</v>
       </c>
       <c r="E461">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F461" t="b">
         <v>0</v>
@@ -13500,7 +13576,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>612</v>
       </c>
@@ -13508,7 +13584,7 @@
         <v>1</v>
       </c>
       <c r="C462">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D462">
         <v>0</v>
@@ -13523,7 +13599,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>613</v>
       </c>
@@ -13531,13 +13607,13 @@
         <v>1</v>
       </c>
       <c r="C463">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D463">
         <v>0</v>
       </c>
       <c r="E463">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F463" t="b">
         <v>0</v>
@@ -13546,7 +13622,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>615</v>
       </c>
@@ -13554,7 +13630,7 @@
         <v>1</v>
       </c>
       <c r="C464">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D464">
         <v>0</v>
@@ -13569,7 +13645,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>617</v>
       </c>
@@ -13577,7 +13653,7 @@
         <v>1</v>
       </c>
       <c r="C465">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D465">
         <v>0</v>
@@ -13592,7 +13668,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>618</v>
       </c>
@@ -13600,7 +13676,7 @@
         <v>1</v>
       </c>
       <c r="C466">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D466">
         <v>0</v>
@@ -13615,7 +13691,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>619</v>
       </c>
@@ -13623,7 +13699,7 @@
         <v>1</v>
       </c>
       <c r="C467">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D467">
         <v>0</v>
@@ -13638,7 +13714,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>621</v>
       </c>
@@ -13646,7 +13722,7 @@
         <v>1</v>
       </c>
       <c r="C468">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D468">
         <v>0</v>
@@ -13661,7 +13737,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>622</v>
       </c>
@@ -13669,7 +13745,7 @@
         <v>1</v>
       </c>
       <c r="C469">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D469">
         <v>0</v>
@@ -13684,7 +13760,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>623</v>
       </c>
@@ -13692,7 +13768,7 @@
         <v>1</v>
       </c>
       <c r="C470">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D470">
         <v>0</v>
@@ -13707,7 +13783,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>624</v>
       </c>
@@ -13715,7 +13791,7 @@
         <v>1</v>
       </c>
       <c r="C471">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D471">
         <v>0</v>
@@ -13730,7 +13806,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>625</v>
       </c>
@@ -13738,7 +13814,7 @@
         <v>1</v>
       </c>
       <c r="C472">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D472">
         <v>0</v>
@@ -13753,7 +13829,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>626</v>
       </c>
@@ -13761,7 +13837,7 @@
         <v>1</v>
       </c>
       <c r="C473">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D473">
         <v>0</v>
@@ -13776,7 +13852,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>627</v>
       </c>
@@ -13799,7 +13875,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>628</v>
       </c>
@@ -13822,7 +13898,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>629</v>
       </c>
@@ -13830,7 +13906,7 @@
         <v>1</v>
       </c>
       <c r="C476">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D476">
         <v>0</v>
@@ -13845,7 +13921,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>630</v>
       </c>
@@ -13853,7 +13929,7 @@
         <v>1</v>
       </c>
       <c r="C477">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D477">
         <v>0</v>
@@ -13868,7 +13944,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>631</v>
       </c>
@@ -13876,7 +13952,7 @@
         <v>1</v>
       </c>
       <c r="C478">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D478">
         <v>0</v>
@@ -13891,7 +13967,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>632</v>
       </c>
@@ -13899,7 +13975,7 @@
         <v>1</v>
       </c>
       <c r="C479">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D479">
         <v>0</v>
@@ -13914,7 +13990,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>633</v>
       </c>
@@ -13922,13 +13998,13 @@
         <v>1</v>
       </c>
       <c r="C480">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D480">
         <v>0</v>
       </c>
       <c r="E480">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F480" t="b">
         <v>0</v>
@@ -13937,7 +14013,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>635</v>
       </c>
@@ -13945,7 +14021,7 @@
         <v>1</v>
       </c>
       <c r="C481">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D481">
         <v>0</v>
@@ -13960,7 +14036,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>636</v>
       </c>
@@ -13968,7 +14044,7 @@
         <v>1</v>
       </c>
       <c r="C482">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D482">
         <v>0</v>
@@ -13983,7 +14059,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>637</v>
       </c>
@@ -13991,7 +14067,7 @@
         <v>1</v>
       </c>
       <c r="C483">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D483">
         <v>0</v>
@@ -14006,7 +14082,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>638</v>
       </c>
@@ -14014,7 +14090,7 @@
         <v>1</v>
       </c>
       <c r="C484">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D484">
         <v>0</v>
@@ -14029,7 +14105,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>639</v>
       </c>
@@ -14037,7 +14113,7 @@
         <v>1</v>
       </c>
       <c r="C485">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D485">
         <v>0</v>
@@ -14052,7 +14128,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>640</v>
       </c>
@@ -14060,13 +14136,13 @@
         <v>1</v>
       </c>
       <c r="C486">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D486">
         <v>0</v>
       </c>
       <c r="E486">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F486" t="b">
         <v>0</v>
@@ -14075,7 +14151,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>642</v>
       </c>
@@ -14083,7 +14159,7 @@
         <v>1</v>
       </c>
       <c r="C487">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D487">
         <v>0</v>
@@ -14098,7 +14174,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>643</v>
       </c>
@@ -14106,7 +14182,7 @@
         <v>1</v>
       </c>
       <c r="C488">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D488">
         <v>0</v>
@@ -14121,7 +14197,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>644</v>
       </c>
@@ -14129,7 +14205,7 @@
         <v>1</v>
       </c>
       <c r="C489">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D489">
         <v>0</v>
@@ -14144,7 +14220,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>645</v>
       </c>
@@ -14152,7 +14228,7 @@
         <v>1</v>
       </c>
       <c r="C490">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D490">
         <v>0</v>
@@ -14167,7 +14243,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>646</v>
       </c>
@@ -14175,7 +14251,7 @@
         <v>1</v>
       </c>
       <c r="C491">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D491">
         <v>0</v>
@@ -14190,7 +14266,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>647</v>
       </c>
@@ -14198,7 +14274,7 @@
         <v>1</v>
       </c>
       <c r="C492">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D492">
         <v>0</v>
@@ -14213,7 +14289,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>648</v>
       </c>
@@ -14221,13 +14297,13 @@
         <v>1</v>
       </c>
       <c r="C493">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D493">
         <v>0</v>
       </c>
       <c r="E493">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F493" t="b">
         <v>0</v>
@@ -14236,7 +14312,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>649</v>
       </c>
@@ -14244,7 +14320,7 @@
         <v>1</v>
       </c>
       <c r="C494">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D494">
         <v>0</v>
@@ -14259,7 +14335,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>650</v>
       </c>
@@ -14267,7 +14343,7 @@
         <v>1</v>
       </c>
       <c r="C495">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D495">
         <v>0</v>
@@ -14282,7 +14358,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>651</v>
       </c>
@@ -14290,7 +14366,7 @@
         <v>1</v>
       </c>
       <c r="C496">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D496">
         <v>0</v>
@@ -14305,7 +14381,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>653</v>
       </c>
@@ -14313,7 +14389,7 @@
         <v>1</v>
       </c>
       <c r="C497">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D497">
         <v>0</v>
@@ -14328,7 +14404,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>654</v>
       </c>
@@ -14336,7 +14412,7 @@
         <v>1</v>
       </c>
       <c r="C498">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D498">
         <v>0</v>
@@ -14351,7 +14427,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>655</v>
       </c>
@@ -14359,7 +14435,7 @@
         <v>1</v>
       </c>
       <c r="C499">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D499">
         <v>0</v>
@@ -14374,7 +14450,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>657</v>
       </c>
@@ -14382,7 +14458,7 @@
         <v>1</v>
       </c>
       <c r="C500">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D500">
         <v>0</v>
@@ -14397,7 +14473,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>658</v>
       </c>
@@ -14405,7 +14481,7 @@
         <v>1</v>
       </c>
       <c r="C501">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D501">
         <v>0</v>
@@ -14420,7 +14496,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>659</v>
       </c>
@@ -14428,13 +14504,13 @@
         <v>1</v>
       </c>
       <c r="C502">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D502">
         <v>0</v>
       </c>
       <c r="E502">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F502" t="b">
         <v>0</v>
@@ -14443,7 +14519,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>660</v>
       </c>
@@ -14451,7 +14527,7 @@
         <v>1</v>
       </c>
       <c r="C503">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D503">
         <v>0</v>
@@ -14466,7 +14542,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>661</v>
       </c>
@@ -14474,7 +14550,7 @@
         <v>1</v>
       </c>
       <c r="C504">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D504">
         <v>0</v>
@@ -14489,7 +14565,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>662</v>
       </c>
@@ -14497,7 +14573,7 @@
         <v>1</v>
       </c>
       <c r="C505">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D505">
         <v>0</v>
@@ -14512,7 +14588,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>663</v>
       </c>
@@ -14520,7 +14596,7 @@
         <v>1</v>
       </c>
       <c r="C506">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D506">
         <v>0</v>
@@ -14535,7 +14611,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>664</v>
       </c>
@@ -14543,7 +14619,7 @@
         <v>1</v>
       </c>
       <c r="C507">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D507">
         <v>7</v>
@@ -14558,7 +14634,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>666</v>
       </c>
@@ -14581,7 +14657,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>668</v>
       </c>
@@ -14604,7 +14680,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>669</v>
       </c>
@@ -14627,7 +14703,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>670</v>
       </c>
@@ -14635,10 +14711,10 @@
         <v>1</v>
       </c>
       <c r="C511">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D511">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E511">
         <v>34</v>
@@ -14650,7 +14726,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>672</v>
       </c>
@@ -14673,7 +14749,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>674</v>
       </c>
@@ -14696,7 +14772,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>675</v>
       </c>
@@ -14719,7 +14795,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>676</v>
       </c>
@@ -14742,7 +14818,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>677</v>
       </c>
@@ -14765,7 +14841,89 @@
         <v>673</v>
       </c>
     </row>
+    <row r="521" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H521" t="s">
+        <v>678</v>
+      </c>
+      <c r="J521" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="522" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H522" s="2">
+        <v>0</v>
+      </c>
+      <c r="I522" s="3">
+        <v>7</v>
+      </c>
+      <c r="J522" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H523" t="s">
+        <v>680</v>
+      </c>
+      <c r="I523" t="s">
+        <v>681</v>
+      </c>
+      <c r="J523" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="525" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H525" t="s">
+        <v>683</v>
+      </c>
+      <c r="I525" t="s">
+        <v>684</v>
+      </c>
+      <c r="J525">
+        <f>I522/(I522+J522)</f>
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="526" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H526" t="s">
+        <v>685</v>
+      </c>
+      <c r="I526" t="s">
+        <v>686</v>
+      </c>
+      <c r="J526">
+        <f>I522/(I522+H522)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H528" t="s">
+        <v>687</v>
+      </c>
+      <c r="I528" t="s">
+        <v>688</v>
+      </c>
+      <c r="L528">
+        <f>2* (J525*J526) /(J525+J526)</f>
+        <v>0.93333333333333335</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:G516">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="TRUE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>